--- a/www/flightdata/xlsx/eoss-373.xlsx
+++ b/www/flightdata/xlsx/eoss-373.xlsx
@@ -3483,7 +3483,7 @@
         <v>30407.76</v>
       </c>
       <c r="I2">
-        <v>679</v>
+        <v>444</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
